--- a/04_DESIGN_TABLES/DesignTable_2601.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2601.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -616,7 +616,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=0.89~0.890; M2@DRIVE=0.89~0.890; N@DRIVE=0.78~0.780; Y@REF=0.44~0.438; D1@BORE=0.17~0.172; D2@BORE=0.17~0.172; DDRILL@BORE=0.19~0.188</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -743,7 +747,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -753,7 +757,7 @@
       </c>
       <c r="P5" s="4" t="inlineStr">
         <is>
-          <t>M legs 1.05 exceed non-FG 0.95 (FG &gt; non-FG, unusual) - as-printed</t>
+          <t>M legs 1.05 exceed non-FG 0.95 (FG &gt; non-FG, unusual) - as-printed | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.05~1.050; M2@DRIVE=1.05~1.050; N@DRIVE=1.09~1.090; Y@REF=0.56~0.562; D1@BORE=0.17~0.172; D2@BORE=0.17~0.172; DDRILL@BORE=0.28~0.281</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1016,7 +1020,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1024,7 +1028,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.06~1.060; M2@DRIVE=1.06~1.060; N@DRIVE=1.09~1.090; Y@REF=0.56~0.562; D1@BORE=0.3~0.297; D2@BORE=0.3~0.297; DDRILL@BORE=0.28~0.281</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1151,7 +1159,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
@@ -1159,7 +1167,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.14~1.140; M2@DRIVE=1.14~1.140; N@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.3~0.297; D2@BORE=0.3~0.297; DDRILL@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1420,7 +1432,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -1428,7 +1440,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.25~1.250; M2@DRIVE=1.25~1.250; N@DRIVE=1.22~1.220; Y@REF=0.75~0.750; D1@BORE=0.39~0.391; D2@BORE=0.39~0.391; DDRILL@BORE=0.41~0.406</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1555,7 +1571,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
@@ -1563,7 +1579,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.33~1.330; M2@DRIVE=1.33~1.330; N@DRIVE=1.47~1.470; Y@REF=0.88~0.875; D1@BORE=0.39~0.391; D2@BORE=0.39~0.391; DDRILL@BORE=0.53~0.531</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2025,7 +2045,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -2033,7 +2053,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.66~1.660; M2@DRIVE=1.66~1.660; N@DRIVE=1.59~1.590; Y@REF=1.06~1.062; D1@BORE=0.61~0.609; D2@BORE=0.61~0.609; DDRILL@BORE=0.72~0.719</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2294,7 +2318,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -2302,7 +2326,11 @@
           <t>Air-Way s170 only (double-pass 29 rows; survey said 28 - page wins); JIC ends VERIFIED (MS33656J); MS51512 exists, untranscribed</t>
         </is>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=1.81~1.810; M2@DRIVE=1.81~1.810; N@DRIVE=1.97~1.970; Y@REF=1.31~1.312; D1@BORE=0.84~0.844; D2@BORE=0.84~0.844; DDRILL@BORE=0.94~0.938</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -2429,7 +2457,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
@@ -2439,7 +2467,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>B(2) printed "1 5/4-12" both passes (typo for 1 5/8-12) - corrected thread used, as-printed in note</t>
+          <t>B(2) printed "1 5/4-12" both passes (typo for 1 5/8-12) - corrected thread used, as-printed in note | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on M1@DRIVE=2.06~2.060; M2@DRIVE=2.06~2.060; N@DRIVE=2.38~2.380; Y@REF=1.63~1.625; D1@BORE=1.08~1.078; D2@BORE=1.08~1.078; DDRILL@BORE=1.25~1.25</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
